--- a/Splunk Basic_2 days.xlsx
+++ b/Splunk Basic_2 days.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29727"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://niit-my.sharepoint.com/personal/angad_bedi_in_niit_com/Documents/Back u p/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\VK_GIT\CISCO_IN_SPLK_11_05_2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{00EDB7E7-9BDB-4BDF-AC18-76BBC80BDF62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D877C5B7-6234-4D57-AC11-8A65A1FAACCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -245,7 +245,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="7">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -294,12 +294,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -331,7 +337,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -358,6 +364,9 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -682,14 +691,14 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="34.28515625" defaultRowHeight="13.9"/>
+  <sheetFormatPr defaultColWidth="34.33203125" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.7109375" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="44.140625" style="3" customWidth="1"/>
-    <col min="4" max="16384" width="34.28515625" style="3"/>
+    <col min="1" max="1" width="16.6640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="44.109375" style="3" customWidth="1"/>
+    <col min="4" max="16384" width="34.33203125" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="27.6" customHeight="1">
+    <row r="1" spans="1:3" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -698,7 +707,7 @@
       </c>
       <c r="C1" s="8"/>
     </row>
-    <row r="2" spans="1:3" ht="55.15" customHeight="1">
+    <row r="2" spans="1:3" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>2</v>
       </c>
@@ -707,7 +716,7 @@
       </c>
       <c r="C2" s="9"/>
     </row>
-    <row r="3" spans="1:3" ht="173.65" customHeight="1">
+    <row r="3" spans="1:3" ht="173.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>4</v>
       </c>
@@ -716,7 +725,7 @@
       </c>
       <c r="C3" s="7"/>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>6</v>
       </c>
@@ -725,14 +734,14 @@
       </c>
       <c r="C4" s="7"/>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="2"/>
       <c r="B5" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C5" s="6"/>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="2"/>
       <c r="B6" s="5" t="s">
         <v>9</v>
@@ -741,27 +750,27 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="156.6" customHeight="1">
+    <row r="7" spans="1:3" ht="156.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2"/>
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" s="10" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="100.9" customHeight="1">
+    <row r="8" spans="1:3" ht="100.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2"/>
-      <c r="B8" s="1" t="s">
+      <c r="B8" s="10" t="s">
         <v>13</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="99.6" customHeight="1">
+    <row r="9" spans="1:3" ht="99.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="2"/>
-      <c r="B9" s="1" t="s">
+      <c r="B9" s="10" t="s">
         <v>15</v>
       </c>
       <c r="C9" s="1" t="s">
@@ -785,6 +794,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="5b6e755b-8d33-4086-9b6b-a9a4d44f3067" xsi:nil="true"/>
@@ -793,15 +811,6 @@
     </lcf76f155ced4ddcb4097134ff3c332f>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1040,13 +1049,39 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2BBD70FC-0662-442B-827A-19EE87BC7460}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{05AF6782-EA11-4081-AA49-98CFECEA3E00}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{05AF6782-EA11-4081-AA49-98CFECEA3E00}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2BBD70FC-0662-442B-827A-19EE87BC7460}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="5b6e755b-8d33-4086-9b6b-a9a4d44f3067"/>
+    <ds:schemaRef ds:uri="ac015f5f-37cf-480b-8f61-9f6dcabe93df"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F8A327A0-61C1-487A-A7A2-9737E4252783}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F8A327A0-61C1-487A-A7A2-9737E4252783}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="ac015f5f-37cf-480b-8f61-9f6dcabe93df"/>
+    <ds:schemaRef ds:uri="5b6e755b-8d33-4086-9b6b-a9a4d44f3067"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/Splunk Basic_2 days.xlsx
+++ b/Splunk Basic_2 days.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\VK_GIT\CISCO_IN_SPLK_11_05_2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D877C5B7-6234-4D57-AC11-8A65A1FAACCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72C8216D-35D2-4219-8622-2517BB127760}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -354,6 +354,9 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -364,9 +367,6 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -702,44 +702,44 @@
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="8"/>
+      <c r="C1" s="9"/>
     </row>
     <row r="2" spans="1:3" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="9"/>
+      <c r="C2" s="10"/>
     </row>
     <row r="3" spans="1:3" ht="173.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="7"/>
+      <c r="C3" s="8"/>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="7"/>
+      <c r="C4" s="8"/>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="2"/>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="6"/>
+      <c r="C5" s="7"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="2"/>
@@ -752,16 +752,16 @@
     </row>
     <row r="7" spans="1:3" ht="156.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2"/>
-      <c r="B7" s="10" t="s">
+      <c r="B7" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="10" t="s">
+      <c r="C7" s="6" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="100.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" ht="133.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2"/>
-      <c r="B8" s="10" t="s">
+      <c r="B8" s="6" t="s">
         <v>13</v>
       </c>
       <c r="C8" s="1" t="s">
@@ -770,7 +770,7 @@
     </row>
     <row r="9" spans="1:3" ht="99.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="2"/>
-      <c r="B9" s="10" t="s">
+      <c r="B9" s="6" t="s">
         <v>15</v>
       </c>
       <c r="C9" s="1" t="s">
@@ -794,15 +794,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="5b6e755b-8d33-4086-9b6b-a9a4d44f3067" xsi:nil="true"/>
@@ -811,6 +802,15 @@
     </lcf76f155ced4ddcb4097134ff3c332f>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1049,20 +1049,20 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{05AF6782-EA11-4081-AA49-98CFECEA3E00}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2BBD70FC-0662-442B-827A-19EE87BC7460}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="5b6e755b-8d33-4086-9b6b-a9a4d44f3067"/>
     <ds:schemaRef ds:uri="ac015f5f-37cf-480b-8f61-9f6dcabe93df"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{05AF6782-EA11-4081-AA49-98CFECEA3E00}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/Splunk Basic_2 days.xlsx
+++ b/Splunk Basic_2 days.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\VK_GIT\CISCO_IN_SPLK_11_05_2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72C8216D-35D2-4219-8622-2517BB127760}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA1E784B-4F5A-488A-9362-FF34C2BE3C5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -337,11 +337,8 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -693,87 +690,87 @@
   <dimension ref="A1:C9"/>
   <sheetFormatPr defaultColWidth="34.33203125" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.6640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="44.109375" style="3" customWidth="1"/>
-    <col min="4" max="16384" width="34.33203125" style="3"/>
+    <col min="1" max="1" width="16.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="44.109375" style="2" customWidth="1"/>
+    <col min="4" max="16384" width="34.33203125" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="9"/>
+      <c r="C1" s="8"/>
     </row>
     <row r="2" spans="1:3" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="10"/>
+      <c r="C2" s="9"/>
     </row>
     <row r="3" spans="1:3" ht="173.7" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="8"/>
+      <c r="C3" s="7"/>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="8"/>
+      <c r="C4" s="7"/>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" s="2"/>
-      <c r="B5" s="7" t="s">
+      <c r="A5" s="1"/>
+      <c r="B5" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="7"/>
+      <c r="C5" s="6"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" s="2"/>
-      <c r="B6" s="5" t="s">
+      <c r="A6" s="1"/>
+      <c r="B6" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="4" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="156.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="2"/>
-      <c r="B7" s="6" t="s">
+      <c r="A7" s="1"/>
+      <c r="B7" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="5" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="133.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="2"/>
-      <c r="B8" s="6" t="s">
+      <c r="A8" s="1"/>
+      <c r="B8" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C8" s="5" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="99.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="2"/>
-      <c r="B9" s="6" t="s">
+      <c r="A9" s="1"/>
+      <c r="B9" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C9" s="5" t="s">
         <v>16</v>
       </c>
     </row>
@@ -805,15 +802,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101001AF7E30AC51BE24AB98F695D1F646B0D" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="944c3efe05a27205f6f8a21900784054">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="ac015f5f-37cf-480b-8f61-9f6dcabe93df" xmlns:ns3="5b6e755b-8d33-4086-9b6b-a9a4d44f3067" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0bdc8c47fb571a171e530ebc6f1b62f9" ns2:_="" ns3:_="">
     <xsd:import namespace="ac015f5f-37cf-480b-8f61-9f6dcabe93df"/>
@@ -1048,6 +1036,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2BBD70FC-0662-442B-827A-19EE87BC7460}">
   <ds:schemaRefs>
@@ -1060,14 +1057,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{05AF6782-EA11-4081-AA49-98CFECEA3E00}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F8A327A0-61C1-487A-A7A2-9737E4252783}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1084,4 +1073,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{05AF6782-EA11-4081-AA49-98CFECEA3E00}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>